--- a/rFLA300/chapter-08/02_Data_Validation.xlsx
+++ b/rFLA300/chapter-08/02_Data_Validation.xlsx
@@ -34,13 +34,13 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="18"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="12"/>
     </font>
     <font>
@@ -55,7 +55,7 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="14"/>
     </font>
     <font>
@@ -66,7 +66,7 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="16"/>
     </font>
     <font>
@@ -76,7 +76,7 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -89,47 +89,47 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
+        <fgColor rgb="FF1F4E79"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002E75B6"/>
+        <fgColor rgb="FF2E75B6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C55A11"/>
+        <fgColor rgb="FFC55A11"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00375623"/>
+        <fgColor rgb="FF375623"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DEEAF1"/>
+        <fgColor rgb="FFDEEAF1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -143,16 +143,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </left>
       <right style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </right>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </bottom>
     </border>
   </borders>
@@ -231,70 +231,70 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -586,7 +586,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="001F4E79"/>
+    <tabColor rgb="FF1F4E79"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -884,7 +884,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002E75B6"/>
+    <tabColor rgb="FF2E75B6"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1201,7 +1201,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002E75B6"/>
+    <tabColor rgb="FF2E75B6"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1505,7 +1505,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002E75B6"/>
+    <tabColor rgb="FF2E75B6"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1737,7 +1737,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002E75B6"/>
+    <tabColor rgb="FF2E75B6"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -2019,7 +2019,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002E75B6"/>
+    <tabColor rgb="FF2E75B6"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -2289,7 +2289,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00375623"/>
+    <tabColor rgb="FF375623"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
